--- a/reports/daily/nikkei225_ranking_ver7_20260918.xlsx
+++ b/reports/daily/nikkei225_ranking_ver7_20260918.xlsx
@@ -860,7 +860,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>1187</v>
       </c>
       <c r="AV3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>1771</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>1554</v>
       </c>
       <c r="AV5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>4985</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>533.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -1970,7 +1970,7 @@
         <v>1675</v>
       </c>
       <c r="AV8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         <v>2957</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>7158</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -2525,7 +2525,7 @@
         <v>5618</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -2714,7 +2714,7 @@
         <v>8531</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>1833</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>7583</v>
       </c>
       <c r="AV14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         <v>173.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>3654</v>
       </c>
       <c r="AV17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
         <v>1983.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         <v>2309</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -4206,7 +4206,7 @@
         <v>7564</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         <v>20960</v>
       </c>
       <c r="AV21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>4682</v>
       </c>
       <c r="AV22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -4765,7 +4765,7 @@
         <v>16435</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>6834</v>
       </c>
       <c r="AV24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>1820</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>6776</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX28" t="n">
         <v>3.888649734538663</v>
@@ -13464,7 +13464,9 @@
       <c r="I75" t="n">
         <v>4.9</v>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>45.7</v>
+      </c>
       <c r="K75" t="n">
         <v>1.5</v>
       </c>
@@ -18414,28 +18416,14 @@
       <c r="AR104" t="n">
         <v>103</v>
       </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>2503_20260917_02</t>
-        </is>
-      </c>
-      <c r="AT104" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AU104" t="n">
-        <v>2893.5</v>
-      </c>
-      <c r="AV104" t="n">
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AU104" t="inlineStr"/>
+      <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="n">
         <v>0</v>
       </c>
-      <c r="AW104" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX104" t="n">
-        <v>-1.555209953343706</v>
-      </c>
+      <c r="AX104" t="inlineStr"/>
       <c r="AY104" t="n">
         <v>110</v>
       </c>
@@ -18445,11 +18433,7 @@
       <c r="BA104" t="n">
         <v>0.1999999999999886</v>
       </c>
-      <c r="BB104" t="inlineStr">
-        <is>
-          <t>MATURE</t>
-        </is>
-      </c>
+      <c r="BB104" t="inlineStr"/>
       <c r="BC104" t="inlineStr">
         <is>
           <t>SKIP</t>
@@ -37679,7 +37663,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -37864,7 +37848,7 @@
         <v>1187</v>
       </c>
       <c r="AV3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -38049,7 +38033,7 @@
         <v>1771</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -38234,7 +38218,7 @@
         <v>1554</v>
       </c>
       <c r="AV5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -38419,7 +38403,7 @@
         <v>4985</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -38604,7 +38588,7 @@
         <v>533.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -38789,7 +38773,7 @@
         <v>1675</v>
       </c>
       <c r="AV8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -38974,7 +38958,7 @@
         <v>2957</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -39159,7 +39143,7 @@
         <v>7158</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -39344,7 +39328,7 @@
         <v>5618</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -39533,7 +39517,7 @@
         <v>8531</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -39722,7 +39706,7 @@
         <v>1833</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -39907,7 +39891,7 @@
         <v>7583</v>
       </c>
       <c r="AV14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -40092,7 +40076,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -40281,7 +40265,7 @@
         <v>173.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -40470,7 +40454,7 @@
         <v>3654</v>
       </c>
       <c r="AV17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -40655,7 +40639,7 @@
         <v>1983.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -40840,7 +40824,7 @@
         <v>2309</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -41025,7 +41009,7 @@
         <v>7564</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -41210,7 +41194,7 @@
         <v>20960</v>
       </c>
       <c r="AV21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
@@ -41399,7 +41383,7 @@
         <v>4682</v>
       </c>
       <c r="AV22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -41584,7 +41568,7 @@
         <v>16435</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>0</v>
@@ -41773,7 +41757,7 @@
         <v>6834</v>
       </c>
       <c r="AV24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -41958,7 +41942,7 @@
         <v>1820</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -42147,7 +42131,7 @@
         <v>6776</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
         <v>0</v>
@@ -42627,7 +42611,7 @@
         <v>4682</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -45831,7 +45815,7 @@
         <v>6834</v>
       </c>
       <c r="AV2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -46020,7 +46004,7 @@
         <v>1833</v>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -46380,7 +46364,7 @@
         <v>173.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -47082,7 +47066,7 @@
         <v>1734</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -47271,7 +47255,7 @@
         <v>3654</v>
       </c>
       <c r="AV10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -47973,7 +47957,7 @@
         <v>8531</v>
       </c>
       <c r="AV14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -48502,7 +48486,7 @@
         <v>6776</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -49269,7 +49253,7 @@
         <v>1983.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -49458,7 +49442,7 @@
         <v>4682</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -49938,7 +49922,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -50123,7 +50107,7 @@
         <v>1771</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -50308,7 +50292,7 @@
         <v>4985</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -50493,7 +50477,7 @@
         <v>7158</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -50678,7 +50662,7 @@
         <v>5618</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -50867,7 +50851,7 @@
         <v>1833</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -51056,7 +51040,7 @@
         <v>173.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -51241,7 +51225,7 @@
         <v>16435</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>

--- a/reports/daily/nikkei225_ranking_ver7_20260918.xlsx
+++ b/reports/daily/nikkei225_ranking_ver7_20260918.xlsx
@@ -860,7 +860,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>1187</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>1771</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>1554</v>
       </c>
       <c r="AV5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>4985</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-1.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>533.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -1970,7 +1970,7 @@
         <v>1675</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -1979,13 +1979,13 @@
         <v>-1.432835820895517</v>
       </c>
       <c r="AY8" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.800000000000011</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>2957</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -2164,13 +2164,13 @@
         <v>-1.741630030436248</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>7158</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -2349,10 +2349,10 @@
         <v>4.638167085778155</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -2525,7 +2525,7 @@
         <v>5618</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -2534,10 +2534,10 @@
         <v>-0.5695977216091164</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -2714,7 +2714,7 @@
         <v>8531</v>
       </c>
       <c r="AV12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -2723,13 +2723,13 @@
         <v>-0.421990387996718</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>1833</v>
       </c>
       <c r="AV13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2912,13 +2912,13 @@
         <v>4.391707583196935</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>7583</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>-3.54185022026432</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>173.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3471,13 +3471,13 @@
         <v>2.367205542725181</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>3654</v>
       </c>
       <c r="AV17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -3660,13 +3660,13 @@
         <v>-0.9304871373836843</v>
       </c>
       <c r="AY17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>1983.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>1.083942525838166</v>
       </c>
       <c r="AY18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         <v>2309</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -4030,13 +4030,13 @@
         <v>3.226504980511047</v>
       </c>
       <c r="AY19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>7564</v>
       </c>
       <c r="AV20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -4215,10 +4215,10 @@
         <v>2.40613432046537</v>
       </c>
       <c r="AY20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         <v>20960</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
@@ -4400,22 +4400,22 @@
         <v>0.4532442748091503</v>
       </c>
       <c r="AY21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.6999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>MATURE</t>
+          <t>RE-ENTRY</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>4682</v>
       </c>
       <c r="AV22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -4589,13 +4589,13 @@
         <v>2.776591200341727</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>16435</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>0</v>
@@ -4774,10 +4774,10 @@
         <v>5.567386674779429</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>6834</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -4963,13 +4963,13 @@
         <v>0.7609013754755534</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.9000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>1820</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -5148,13 +5148,13 @@
         <v>-1.318681318681314</v>
       </c>
       <c r="AY25" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AZ25" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>-1.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>6776</v>
       </c>
       <c r="AV26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
         <v>0</v>
@@ -5337,13 +5337,13 @@
         <v>0.7969303423848828</v>
       </c>
       <c r="AY26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ26" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
@@ -5666,42 +5666,24 @@
       <c r="AR28" t="n">
         <v>27</v>
       </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>9104_20260904_02</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AU28" t="n">
-        <v>6969</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>9</v>
-      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>3.888649734538663</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AZ28" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>-0.6000000000000085</v>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>MATURE</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="inlineStr">
         <is>
           <t>SKIP</t>
@@ -5860,10 +5842,10 @@
       </c>
       <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
         <v>0</v>
@@ -6027,10 +6009,10 @@
       </c>
       <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
         <v>0</v>
@@ -6198,13 +6180,13 @@
       </c>
       <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr">
@@ -6365,13 +6347,13 @@
       </c>
       <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.8999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr">
@@ -6532,13 +6514,13 @@
       </c>
       <c r="AX33" t="inlineStr"/>
       <c r="AY33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.6000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr">
@@ -6699,13 +6681,13 @@
       </c>
       <c r="AX34" t="inlineStr"/>
       <c r="AY34" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AZ34" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>-0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="inlineStr">
@@ -6866,13 +6848,13 @@
       </c>
       <c r="AX35" t="inlineStr"/>
       <c r="AY35" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="AZ35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="inlineStr">
@@ -7037,13 +7019,13 @@
       </c>
       <c r="AX36" t="inlineStr"/>
       <c r="AY36" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AZ36" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr">
@@ -7208,13 +7190,13 @@
       </c>
       <c r="AX37" t="inlineStr"/>
       <c r="AY37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AZ37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="inlineStr"/>
       <c r="BC37" t="inlineStr">
@@ -7373,13 +7355,13 @@
       </c>
       <c r="AX38" t="inlineStr"/>
       <c r="AY38" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.6000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="inlineStr">
@@ -7538,13 +7520,13 @@
       </c>
       <c r="AX39" t="inlineStr"/>
       <c r="AY39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AZ39" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr">
@@ -7705,13 +7687,13 @@
       </c>
       <c r="AX40" t="inlineStr"/>
       <c r="AY40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="inlineStr"/>
       <c r="BC40" t="inlineStr">
@@ -7872,13 +7854,13 @@
       </c>
       <c r="AX41" t="inlineStr"/>
       <c r="AY41" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AZ41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="inlineStr">
@@ -8039,13 +8021,13 @@
       </c>
       <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="inlineStr">
@@ -8210,13 +8192,13 @@
       </c>
       <c r="AX43" t="inlineStr"/>
       <c r="AY43" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AZ43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="inlineStr"/>
       <c r="BC43" t="inlineStr">
@@ -8377,13 +8359,13 @@
       </c>
       <c r="AX44" t="inlineStr"/>
       <c r="AY44" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.6000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr">
@@ -8548,13 +8530,13 @@
       </c>
       <c r="AX45" t="inlineStr"/>
       <c r="AY45" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AZ45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr">
@@ -8715,13 +8697,13 @@
       </c>
       <c r="AX46" t="inlineStr"/>
       <c r="AY46" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AZ46" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="inlineStr"/>
       <c r="BC46" t="inlineStr">
@@ -8886,13 +8868,13 @@
       </c>
       <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AZ47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="inlineStr">
@@ -9057,13 +9039,13 @@
       </c>
       <c r="AX48" t="inlineStr"/>
       <c r="AY48" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>-0.3000000000000114</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="inlineStr"/>
       <c r="BC48" t="inlineStr">
@@ -9230,7 +9212,7 @@
         <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="inlineStr"/>
       <c r="BC49" t="inlineStr">
@@ -9395,13 +9377,13 @@
       </c>
       <c r="AX50" t="inlineStr"/>
       <c r="AY50" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>-0.1999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB50" t="inlineStr"/>
       <c r="BC50" t="inlineStr">
@@ -9562,13 +9544,13 @@
       </c>
       <c r="AX51" t="inlineStr"/>
       <c r="AY51" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AZ51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.3000000000000114</v>
+        <v>0</v>
       </c>
       <c r="BB51" t="inlineStr"/>
       <c r="BC51" t="inlineStr">
@@ -9729,13 +9711,13 @@
       </c>
       <c r="AX52" t="inlineStr"/>
       <c r="AY52" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AZ52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>-0.1999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="inlineStr"/>
       <c r="BC52" t="inlineStr">
@@ -9896,13 +9878,13 @@
       </c>
       <c r="AX53" t="inlineStr"/>
       <c r="AY53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AZ53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BB53" t="inlineStr"/>
       <c r="BC53" t="inlineStr">
@@ -10234,13 +10216,13 @@
       </c>
       <c r="AX55" t="inlineStr"/>
       <c r="AY55" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AZ55" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BA55" t="n">
-        <v>-1.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="BB55" t="inlineStr"/>
       <c r="BC55" t="inlineStr">
@@ -10401,13 +10383,13 @@
       </c>
       <c r="AX56" t="inlineStr"/>
       <c r="AY56" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AZ56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA56" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB56" t="inlineStr"/>
       <c r="BC56" t="inlineStr">
@@ -10568,13 +10550,13 @@
       </c>
       <c r="AX57" t="inlineStr"/>
       <c r="AY57" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AZ57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA57" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB57" t="inlineStr"/>
       <c r="BC57" t="inlineStr">
@@ -10735,13 +10717,13 @@
       </c>
       <c r="AX58" t="inlineStr"/>
       <c r="AY58" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AZ58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA58" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="inlineStr"/>
       <c r="BC58" t="inlineStr">
@@ -10900,13 +10882,13 @@
       </c>
       <c r="AX59" t="inlineStr"/>
       <c r="AY59" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AZ59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA59" t="n">
-        <v>0.1999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr">
@@ -11067,13 +11049,13 @@
       </c>
       <c r="AX60" t="inlineStr"/>
       <c r="AY60" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AZ60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA60" t="n">
-        <v>-0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="inlineStr">
@@ -11234,13 +11216,13 @@
       </c>
       <c r="AX61" t="inlineStr"/>
       <c r="AY61" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AZ61" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="BA61" t="n">
-        <v>-5.799999999999997</v>
+        <v>0</v>
       </c>
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="inlineStr">
@@ -11399,13 +11381,13 @@
       </c>
       <c r="AX62" t="inlineStr"/>
       <c r="AY62" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AZ62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA62" t="n">
-        <v>-0.5999999999999943</v>
+        <v>0</v>
       </c>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr">
@@ -11566,13 +11548,13 @@
       </c>
       <c r="AX63" t="inlineStr"/>
       <c r="AY63" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="AZ63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA63" t="n">
-        <v>0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB63" t="inlineStr"/>
       <c r="BC63" t="inlineStr">
@@ -11731,13 +11713,13 @@
       </c>
       <c r="AX64" t="inlineStr"/>
       <c r="AY64" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AZ64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA64" t="n">
-        <v>-0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB64" t="inlineStr"/>
       <c r="BC64" t="inlineStr">
@@ -11898,13 +11880,13 @@
       </c>
       <c r="AX65" t="inlineStr"/>
       <c r="AY65" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AZ65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA65" t="n">
-        <v>-1.100000000000009</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="inlineStr"/>
       <c r="BC65" t="inlineStr">
@@ -12063,13 +12045,13 @@
       </c>
       <c r="AX66" t="inlineStr"/>
       <c r="AY66" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AZ66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="inlineStr"/>
       <c r="BC66" t="inlineStr">
@@ -12230,13 +12212,13 @@
       </c>
       <c r="AX67" t="inlineStr"/>
       <c r="AY67" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AZ67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA67" t="n">
-        <v>0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB67" t="inlineStr"/>
       <c r="BC67" t="inlineStr">
@@ -12397,10 +12379,10 @@
       </c>
       <c r="AX68" t="inlineStr"/>
       <c r="AY68" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AZ68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA68" t="n">
         <v>0</v>
@@ -12568,13 +12550,13 @@
       </c>
       <c r="AX69" t="inlineStr"/>
       <c r="AY69" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="AZ69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA69" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB69" t="inlineStr"/>
       <c r="BC69" t="inlineStr">
@@ -12735,13 +12717,13 @@
       </c>
       <c r="AX70" t="inlineStr"/>
       <c r="AY70" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="AZ70" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA70" t="n">
-        <v>0.5999999999999943</v>
+        <v>0</v>
       </c>
       <c r="BB70" t="inlineStr"/>
       <c r="BC70" t="inlineStr">
@@ -12906,10 +12888,10 @@
       </c>
       <c r="AX71" t="inlineStr"/>
       <c r="AY71" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AZ71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA71" t="n">
         <v>0</v>
@@ -13071,10 +13053,10 @@
       </c>
       <c r="AX72" t="inlineStr"/>
       <c r="AY72" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AZ72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA72" t="n">
         <v>0</v>
@@ -13238,13 +13220,13 @@
       </c>
       <c r="AX73" t="inlineStr"/>
       <c r="AY73" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AZ73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA73" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB73" t="inlineStr"/>
       <c r="BC73" t="inlineStr">
@@ -13409,13 +13391,13 @@
       </c>
       <c r="AX74" t="inlineStr"/>
       <c r="AY74" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AZ74" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA74" t="n">
-        <v>0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB74" t="inlineStr"/>
       <c r="BC74" t="inlineStr">
@@ -13574,10 +13556,10 @@
       </c>
       <c r="AX75" t="inlineStr"/>
       <c r="AY75" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AZ75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA75" t="n">
         <v>0</v>
@@ -13908,13 +13890,13 @@
       </c>
       <c r="AX77" t="inlineStr"/>
       <c r="AY77" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AZ77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA77" t="n">
-        <v>0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB77" t="inlineStr"/>
       <c r="BC77" t="inlineStr">
@@ -14075,13 +14057,13 @@
       </c>
       <c r="AX78" t="inlineStr"/>
       <c r="AY78" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AZ78" t="n">
-        <v>-41</v>
+        <v>0</v>
       </c>
       <c r="BA78" t="n">
-        <v>-10.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB78" t="inlineStr"/>
       <c r="BC78" t="inlineStr">
@@ -14242,13 +14224,13 @@
       </c>
       <c r="AX79" t="inlineStr"/>
       <c r="AY79" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AZ79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA79" t="n">
-        <v>1.300000000000011</v>
+        <v>0</v>
       </c>
       <c r="BB79" t="inlineStr"/>
       <c r="BC79" t="inlineStr">
@@ -14413,13 +14395,13 @@
       </c>
       <c r="AX80" t="inlineStr"/>
       <c r="AY80" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA80" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="inlineStr"/>
       <c r="BC80" t="inlineStr">
@@ -14580,13 +14562,13 @@
       </c>
       <c r="AX81" t="inlineStr"/>
       <c r="AY81" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
-        <v>0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="inlineStr"/>
       <c r="BC81" t="inlineStr">
@@ -14745,10 +14727,10 @@
       </c>
       <c r="AX82" t="inlineStr"/>
       <c r="AY82" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AZ82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
         <v>0</v>
@@ -14912,10 +14894,10 @@
       </c>
       <c r="AX83" t="inlineStr"/>
       <c r="AY83" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AZ83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA83" t="n">
         <v>0</v>
@@ -15079,13 +15061,13 @@
       </c>
       <c r="AX84" t="inlineStr"/>
       <c r="AY84" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="AZ84" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA84" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB84" t="inlineStr"/>
       <c r="BC84" t="inlineStr">
@@ -15246,13 +15228,13 @@
       </c>
       <c r="AX85" t="inlineStr"/>
       <c r="AY85" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AZ85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA85" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB85" t="inlineStr"/>
       <c r="BC85" t="inlineStr">
@@ -15413,13 +15395,13 @@
       </c>
       <c r="AX86" t="inlineStr"/>
       <c r="AY86" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AZ86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA86" t="n">
-        <v>-0.3000000000000114</v>
+        <v>0</v>
       </c>
       <c r="BB86" t="inlineStr"/>
       <c r="BC86" t="inlineStr">
@@ -15580,13 +15562,13 @@
       </c>
       <c r="AX87" t="inlineStr"/>
       <c r="AY87" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="AZ87" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="BA87" t="n">
-        <v>-10.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB87" t="inlineStr"/>
       <c r="BC87" t="inlineStr">
@@ -15753,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>-0.6999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="inlineStr"/>
       <c r="BC88" t="inlineStr">
@@ -15914,10 +15896,10 @@
       </c>
       <c r="AX89" t="inlineStr"/>
       <c r="AY89" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AZ89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA89" t="n">
         <v>0</v>
@@ -16085,13 +16067,13 @@
       </c>
       <c r="AX90" t="inlineStr"/>
       <c r="AY90" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AZ90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA90" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="inlineStr"/>
       <c r="BC90" t="inlineStr">
@@ -16258,7 +16240,7 @@
         <v>0</v>
       </c>
       <c r="BA91" t="n">
-        <v>-1.100000000000009</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="inlineStr"/>
       <c r="BC91" t="inlineStr">
@@ -16419,13 +16401,13 @@
       </c>
       <c r="AX92" t="inlineStr"/>
       <c r="AY92" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AZ92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA92" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BB92" t="inlineStr"/>
       <c r="BC92" t="inlineStr">
@@ -16586,13 +16568,13 @@
       </c>
       <c r="AX93" t="inlineStr"/>
       <c r="AY93" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA93" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB93" t="inlineStr"/>
       <c r="BC93" t="inlineStr">
@@ -16753,13 +16735,13 @@
       </c>
       <c r="AX94" t="inlineStr"/>
       <c r="AY94" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AZ94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA94" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BB94" t="inlineStr"/>
       <c r="BC94" t="inlineStr">
@@ -16920,13 +16902,13 @@
       </c>
       <c r="AX95" t="inlineStr"/>
       <c r="AY95" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AZ95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA95" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB95" t="inlineStr"/>
       <c r="BC95" t="inlineStr">
@@ -17087,13 +17069,13 @@
       </c>
       <c r="AX96" t="inlineStr"/>
       <c r="AY96" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AZ96" t="n">
-        <v>-39</v>
+        <v>0</v>
       </c>
       <c r="BA96" t="n">
-        <v>-11.39999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB96" t="inlineStr"/>
       <c r="BC96" t="inlineStr">
@@ -17254,13 +17236,13 @@
       </c>
       <c r="AX97" t="inlineStr"/>
       <c r="AY97" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AZ97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA97" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB97" t="inlineStr"/>
       <c r="BC97" t="inlineStr">
@@ -17421,13 +17403,13 @@
       </c>
       <c r="AX98" t="inlineStr"/>
       <c r="AY98" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AZ98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA98" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB98" t="inlineStr"/>
       <c r="BC98" t="inlineStr">
@@ -17586,13 +17568,13 @@
       </c>
       <c r="AX99" t="inlineStr"/>
       <c r="AY99" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AZ99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA99" t="n">
-        <v>0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB99" t="inlineStr"/>
       <c r="BC99" t="inlineStr">
@@ -17753,13 +17735,13 @@
       </c>
       <c r="AX100" t="inlineStr"/>
       <c r="AY100" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="AZ100" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="BA100" t="n">
-        <v>-10.8</v>
+        <v>0</v>
       </c>
       <c r="BB100" t="inlineStr"/>
       <c r="BC100" t="inlineStr">
@@ -18091,13 +18073,13 @@
       </c>
       <c r="AX102" t="inlineStr"/>
       <c r="AY102" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AZ102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA102" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB102" t="inlineStr"/>
       <c r="BC102" t="inlineStr">
@@ -18258,13 +18240,13 @@
       </c>
       <c r="AX103" t="inlineStr"/>
       <c r="AY103" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AZ103" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA103" t="n">
-        <v>-0.9000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB103" t="inlineStr"/>
       <c r="BC103" t="inlineStr">
@@ -18588,10 +18570,10 @@
       </c>
       <c r="AX105" t="inlineStr"/>
       <c r="AY105" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="AZ105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA105" t="n">
         <v>0</v>
@@ -18755,10 +18737,10 @@
       </c>
       <c r="AX106" t="inlineStr"/>
       <c r="AY106" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AZ106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA106" t="n">
         <v>0</v>
@@ -19256,13 +19238,13 @@
       </c>
       <c r="AX109" t="inlineStr"/>
       <c r="AY109" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="AZ109" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BA109" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BB109" t="inlineStr"/>
       <c r="BC109" t="inlineStr">
@@ -19590,13 +19572,13 @@
       </c>
       <c r="AX111" t="inlineStr"/>
       <c r="AY111" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AZ111" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="BA111" t="n">
-        <v>-1.700000000000003</v>
+        <v>0</v>
       </c>
       <c r="BB111" t="inlineStr"/>
       <c r="BC111" t="inlineStr">
@@ -19757,10 +19739,10 @@
       </c>
       <c r="AX112" t="inlineStr"/>
       <c r="AY112" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AZ112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA112" t="n">
         <v>0</v>
@@ -19928,7 +19910,7 @@
         <v>0</v>
       </c>
       <c r="BA113" t="n">
-        <v>-0.7999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB113" t="inlineStr"/>
       <c r="BC113" t="inlineStr">
@@ -20087,13 +20069,13 @@
       </c>
       <c r="AX114" t="inlineStr"/>
       <c r="AY114" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AZ114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA114" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB114" t="inlineStr"/>
       <c r="BC114" t="inlineStr">
@@ -20256,13 +20238,13 @@
       </c>
       <c r="AX115" t="inlineStr"/>
       <c r="AY115" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="AZ115" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA115" t="n">
-        <v>1.200000000000003</v>
+        <v>0</v>
       </c>
       <c r="BB115" t="inlineStr"/>
       <c r="BC115" t="inlineStr">
@@ -20421,13 +20403,13 @@
       </c>
       <c r="AX116" t="inlineStr"/>
       <c r="AY116" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="AZ116" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BA116" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BB116" t="inlineStr"/>
       <c r="BC116" t="inlineStr">
@@ -20588,10 +20570,10 @@
       </c>
       <c r="AX117" t="inlineStr"/>
       <c r="AY117" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AZ117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA117" t="n">
         <v>0</v>
@@ -20757,13 +20739,13 @@
       </c>
       <c r="AX118" t="inlineStr"/>
       <c r="AY118" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AZ118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA118" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BB118" t="inlineStr"/>
       <c r="BC118" t="inlineStr">
@@ -20924,13 +20906,13 @@
       </c>
       <c r="AX119" t="inlineStr"/>
       <c r="AY119" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="AZ119" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="inlineStr"/>
       <c r="BC119" t="inlineStr">
@@ -21089,13 +21071,13 @@
       </c>
       <c r="AX120" t="inlineStr"/>
       <c r="AY120" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AZ120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA120" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB120" t="inlineStr"/>
       <c r="BC120" t="inlineStr">
@@ -21256,10 +21238,10 @@
       </c>
       <c r="AX121" t="inlineStr"/>
       <c r="AY121" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AZ121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA121" t="n">
         <v>0</v>
@@ -21423,10 +21405,10 @@
       </c>
       <c r="AX122" t="inlineStr"/>
       <c r="AY122" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AZ122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA122" t="n">
         <v>0</v>
@@ -21586,13 +21568,13 @@
       </c>
       <c r="AX123" t="inlineStr"/>
       <c r="AY123" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AZ123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA123" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB123" t="inlineStr"/>
       <c r="BC123" t="inlineStr">
@@ -21753,13 +21735,13 @@
       </c>
       <c r="AX124" t="inlineStr"/>
       <c r="AY124" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="AZ124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA124" t="n">
-        <v>-0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB124" t="inlineStr"/>
       <c r="BC124" t="inlineStr">
@@ -21924,13 +21906,13 @@
       </c>
       <c r="AX125" t="inlineStr"/>
       <c r="AY125" t="n">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="AZ125" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BA125" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BB125" t="inlineStr"/>
       <c r="BC125" t="inlineStr">
@@ -22091,10 +22073,10 @@
       </c>
       <c r="AX126" t="inlineStr"/>
       <c r="AY126" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AZ126" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BA126" t="n">
         <v>0</v>
@@ -22258,13 +22240,13 @@
       </c>
       <c r="AX127" t="inlineStr"/>
       <c r="AY127" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="AZ127" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BA127" t="n">
-        <v>-0.3000000000000114</v>
+        <v>0</v>
       </c>
       <c r="BB127" t="inlineStr"/>
       <c r="BC127" t="inlineStr">
@@ -22425,13 +22407,13 @@
       </c>
       <c r="AX128" t="inlineStr"/>
       <c r="AY128" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="AZ128" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BA128" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB128" t="inlineStr"/>
       <c r="BC128" t="inlineStr">
@@ -22586,13 +22568,13 @@
       </c>
       <c r="AX129" t="inlineStr"/>
       <c r="AY129" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="AZ129" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA129" t="n">
-        <v>0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB129" t="inlineStr"/>
       <c r="BC129" t="inlineStr">
@@ -22751,13 +22733,13 @@
       </c>
       <c r="AX130" t="inlineStr"/>
       <c r="AY130" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AZ130" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA130" t="n">
-        <v>-0.5999999999999943</v>
+        <v>0</v>
       </c>
       <c r="BB130" t="inlineStr"/>
       <c r="BC130" t="inlineStr">
@@ -22918,13 +22900,13 @@
       </c>
       <c r="AX131" t="inlineStr"/>
       <c r="AY131" t="n">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="AZ131" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="BA131" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="BB131" t="inlineStr"/>
       <c r="BC131" t="inlineStr">
@@ -23083,13 +23065,13 @@
       </c>
       <c r="AX132" t="inlineStr"/>
       <c r="AY132" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="AZ132" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA132" t="n">
-        <v>-0.8000000000000114</v>
+        <v>0</v>
       </c>
       <c r="BB132" t="inlineStr"/>
       <c r="BC132" t="inlineStr">
@@ -23254,13 +23236,13 @@
       </c>
       <c r="AX133" t="inlineStr"/>
       <c r="AY133" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="AZ133" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="BA133" t="n">
-        <v>-10.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB133" t="inlineStr"/>
       <c r="BC133" t="inlineStr">
@@ -23421,13 +23403,13 @@
       </c>
       <c r="AX134" t="inlineStr"/>
       <c r="AY134" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="AZ134" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="BA134" t="n">
-        <v>-10.39999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB134" t="inlineStr"/>
       <c r="BC134" t="inlineStr">
@@ -23588,13 +23570,13 @@
       </c>
       <c r="AX135" t="inlineStr"/>
       <c r="AY135" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="AZ135" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA135" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB135" t="inlineStr"/>
       <c r="BC135" t="inlineStr">
@@ -23755,10 +23737,10 @@
       </c>
       <c r="AX136" t="inlineStr"/>
       <c r="AY136" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="AZ136" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA136" t="n">
         <v>0</v>
@@ -23922,10 +23904,10 @@
       </c>
       <c r="AX137" t="inlineStr"/>
       <c r="AY137" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="AZ137" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA137" t="n">
         <v>0</v>
@@ -24091,13 +24073,13 @@
       </c>
       <c r="AX138" t="inlineStr"/>
       <c r="AY138" t="n">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="AZ138" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="BA138" t="n">
-        <v>11.00000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB138" t="inlineStr"/>
       <c r="BC138" t="inlineStr">
@@ -24258,10 +24240,10 @@
       </c>
       <c r="AX139" t="inlineStr"/>
       <c r="AY139" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AZ139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA139" t="n">
         <v>0</v>
@@ -24423,13 +24405,13 @@
       </c>
       <c r="AX140" t="inlineStr"/>
       <c r="AY140" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="AZ140" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="BA140" t="n">
-        <v>-10.5</v>
+        <v>0</v>
       </c>
       <c r="BB140" t="inlineStr"/>
       <c r="BC140" t="inlineStr">
@@ -24590,10 +24572,10 @@
       </c>
       <c r="AX141" t="inlineStr"/>
       <c r="AY141" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AZ141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA141" t="n">
         <v>0</v>
@@ -24761,10 +24743,10 @@
       </c>
       <c r="AX142" t="inlineStr"/>
       <c r="AY142" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AZ142" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA142" t="n">
         <v>0</v>
@@ -24928,13 +24910,13 @@
       </c>
       <c r="AX143" t="inlineStr"/>
       <c r="AY143" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="AZ143" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="BA143" t="n">
-        <v>-10.60000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB143" t="inlineStr"/>
       <c r="BC143" t="inlineStr">
@@ -25091,13 +25073,13 @@
       </c>
       <c r="AX144" t="inlineStr"/>
       <c r="AY144" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AZ144" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA144" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB144" t="inlineStr"/>
       <c r="BC144" t="inlineStr">
@@ -25258,13 +25240,13 @@
       </c>
       <c r="AX145" t="inlineStr"/>
       <c r="AY145" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AZ145" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BB145" t="inlineStr"/>
       <c r="BC145" t="inlineStr">
@@ -25425,13 +25407,13 @@
       </c>
       <c r="AX146" t="inlineStr"/>
       <c r="AY146" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AZ146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA146" t="n">
-        <v>-0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB146" t="inlineStr"/>
       <c r="BC146" t="inlineStr">
@@ -25588,13 +25570,13 @@
       </c>
       <c r="AX147" t="inlineStr"/>
       <c r="AY147" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AZ147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA147" t="n">
-        <v>-1.600000000000009</v>
+        <v>0</v>
       </c>
       <c r="BB147" t="inlineStr"/>
       <c r="BC147" t="inlineStr">
@@ -25755,10 +25737,10 @@
       </c>
       <c r="AX148" t="inlineStr"/>
       <c r="AY148" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AZ148" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA148" t="n">
         <v>0</v>
@@ -25922,10 +25904,10 @@
       </c>
       <c r="AX149" t="inlineStr"/>
       <c r="AY149" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AZ149" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA149" t="n">
         <v>0</v>
@@ -26083,13 +26065,13 @@
       </c>
       <c r="AX150" t="inlineStr"/>
       <c r="AY150" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AZ150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA150" t="n">
-        <v>-1.199999999999989</v>
+        <v>0</v>
       </c>
       <c r="BB150" t="inlineStr"/>
       <c r="BC150" t="inlineStr">
@@ -26252,13 +26234,13 @@
       </c>
       <c r="AX151" t="inlineStr"/>
       <c r="AY151" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="AZ151" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA151" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB151" t="inlineStr"/>
       <c r="BC151" t="inlineStr">
@@ -26419,13 +26401,13 @@
       </c>
       <c r="AX152" t="inlineStr"/>
       <c r="AY152" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AZ152" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA152" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB152" t="inlineStr"/>
       <c r="BC152" t="inlineStr">
@@ -26586,13 +26568,13 @@
       </c>
       <c r="AX153" t="inlineStr"/>
       <c r="AY153" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AZ153" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA153" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB153" t="inlineStr"/>
       <c r="BC153" t="inlineStr">
@@ -26747,13 +26729,13 @@
       </c>
       <c r="AX154" t="inlineStr"/>
       <c r="AY154" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AZ154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA154" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB154" t="inlineStr"/>
       <c r="BC154" t="inlineStr">
@@ -26912,13 +26894,13 @@
       </c>
       <c r="AX155" t="inlineStr"/>
       <c r="AY155" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AZ155" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA155" t="n">
-        <v>0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB155" t="inlineStr"/>
       <c r="BC155" t="inlineStr">
@@ -27077,13 +27059,13 @@
       </c>
       <c r="AX156" t="inlineStr"/>
       <c r="AY156" t="n">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="AZ156" t="n">
-        <v>-46</v>
+        <v>0</v>
       </c>
       <c r="BA156" t="n">
-        <v>-17.7</v>
+        <v>0</v>
       </c>
       <c r="BB156" t="inlineStr"/>
       <c r="BC156" t="inlineStr">
@@ -27244,13 +27226,13 @@
       </c>
       <c r="AX157" t="inlineStr"/>
       <c r="AY157" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AZ157" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="BA157" t="n">
-        <v>-5.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="BB157" t="inlineStr"/>
       <c r="BC157" t="inlineStr">
@@ -27411,13 +27393,13 @@
       </c>
       <c r="AX158" t="inlineStr"/>
       <c r="AY158" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="AZ158" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="BA158" t="n">
-        <v>-11.3</v>
+        <v>0</v>
       </c>
       <c r="BB158" t="inlineStr"/>
       <c r="BC158" t="inlineStr">
@@ -27578,10 +27560,10 @@
       </c>
       <c r="AX159" t="inlineStr"/>
       <c r="AY159" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AZ159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA159" t="n">
         <v>0</v>
@@ -27745,13 +27727,13 @@
       </c>
       <c r="AX160" t="inlineStr"/>
       <c r="AY160" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AZ160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA160" t="n">
-        <v>-0.1999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB160" t="inlineStr"/>
       <c r="BC160" t="inlineStr">
@@ -27912,13 +27894,13 @@
       </c>
       <c r="AX161" t="inlineStr"/>
       <c r="AY161" t="n">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="AZ161" t="n">
-        <v>-66</v>
+        <v>0</v>
       </c>
       <c r="BA161" t="n">
-        <v>-22.10000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB161" t="inlineStr"/>
       <c r="BC161" t="inlineStr">
@@ -28079,10 +28061,10 @@
       </c>
       <c r="AX162" t="inlineStr"/>
       <c r="AY162" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AZ162" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA162" t="n">
         <v>0</v>
@@ -29906,13 +29888,13 @@
       </c>
       <c r="AX173" t="inlineStr"/>
       <c r="AY173" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="AZ173" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="BA173" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="BB173" t="inlineStr"/>
       <c r="BC173" t="inlineStr">
@@ -30401,13 +30383,13 @@
       </c>
       <c r="AX176" t="inlineStr"/>
       <c r="AY176" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AZ176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA176" t="n">
-        <v>0.1999999999999957</v>
+        <v>0</v>
       </c>
       <c r="BB176" t="inlineStr"/>
       <c r="BC176" t="inlineStr">
@@ -37663,7 +37645,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -37678,7 +37660,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -37848,7 +37830,7 @@
         <v>1187</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -38033,7 +38015,7 @@
         <v>1771</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -38048,7 +38030,7 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -38218,7 +38200,7 @@
         <v>1554</v>
       </c>
       <c r="AV5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -38233,7 +38215,7 @@
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -38403,7 +38385,7 @@
         <v>4985</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -38418,7 +38400,7 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-1.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -38588,7 +38570,7 @@
         <v>533.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -38773,7 +38755,7 @@
         <v>1675</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -38782,13 +38764,13 @@
         <v>-1.432835820895517</v>
       </c>
       <c r="AY8" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.800000000000011</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -38958,7 +38940,7 @@
         <v>2957</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -38967,13 +38949,13 @@
         <v>-1.741630030436248</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -39143,7 +39125,7 @@
         <v>7158</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -39152,10 +39134,10 @@
         <v>4.638167085778155</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -39328,7 +39310,7 @@
         <v>5618</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -39337,10 +39319,10 @@
         <v>-0.5695977216091164</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -39517,7 +39499,7 @@
         <v>8531</v>
       </c>
       <c r="AV12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -39526,13 +39508,13 @@
         <v>-0.421990387996718</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -39706,7 +39688,7 @@
         <v>1833</v>
       </c>
       <c r="AV13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -39715,13 +39697,13 @@
         <v>4.391707583196935</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
@@ -39891,7 +39873,7 @@
         <v>7583</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -39906,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -40076,7 +40058,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -40085,13 +40067,13 @@
         <v>-3.54185022026432</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
@@ -40265,7 +40247,7 @@
         <v>173.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -40274,13 +40256,13 @@
         <v>2.367205542725181</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
@@ -40454,7 +40436,7 @@
         <v>3654</v>
       </c>
       <c r="AV17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -40463,13 +40445,13 @@
         <v>-0.9304871373836843</v>
       </c>
       <c r="AY17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -40639,7 +40621,7 @@
         <v>1983.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -40648,10 +40630,10 @@
         <v>1.083942525838166</v>
       </c>
       <c r="AY18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -40824,7 +40806,7 @@
         <v>2309</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -40833,13 +40815,13 @@
         <v>3.226504980511047</v>
       </c>
       <c r="AY19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
@@ -41009,7 +40991,7 @@
         <v>7564</v>
       </c>
       <c r="AV20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -41018,10 +41000,10 @@
         <v>2.40613432046537</v>
       </c>
       <c r="AY20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -41194,7 +41176,7 @@
         <v>20960</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
@@ -41203,22 +41185,22 @@
         <v>0.4532442748091503</v>
       </c>
       <c r="AY21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.6999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>MATURE</t>
+          <t>RE-ENTRY</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41365,7 @@
         <v>4682</v>
       </c>
       <c r="AV22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -41392,13 +41374,13 @@
         <v>2.776591200341727</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
@@ -41568,7 +41550,7 @@
         <v>16435</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>0</v>
@@ -41577,10 +41559,10 @@
         <v>5.567386674779429</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -41757,7 +41739,7 @@
         <v>6834</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -41766,13 +41748,13 @@
         <v>0.7609013754755534</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.9000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
@@ -41942,7 +41924,7 @@
         <v>1820</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -41951,13 +41933,13 @@
         <v>-1.318681318681314</v>
       </c>
       <c r="AY25" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AZ25" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>-1.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
@@ -42131,7 +42113,7 @@
         <v>6776</v>
       </c>
       <c r="AV26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
         <v>0</v>
@@ -42140,13 +42122,13 @@
         <v>0.7969303423848828</v>
       </c>
       <c r="AY26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ26" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
@@ -42611,7 +42593,7 @@
         <v>4682</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -42620,13 +42602,13 @@
         <v>2.776591200341727</v>
       </c>
       <c r="AY2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -42795,13 +42777,13 @@
       </c>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
@@ -42966,13 +42948,13 @@
       </c>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
@@ -43308,13 +43290,13 @@
       </c>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr">
@@ -43479,10 +43461,10 @@
       </c>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -43650,13 +43632,13 @@
       </c>
       <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.7000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr">
@@ -43821,13 +43803,13 @@
       </c>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr">
@@ -44161,13 +44143,13 @@
       </c>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.200000000000003</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr">
@@ -44332,13 +44314,13 @@
       </c>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="n">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr">
@@ -44501,13 +44483,13 @@
       </c>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="n">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="AZ13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.00000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr">
@@ -44672,10 +44654,10 @@
       </c>
       <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
         <v>0</v>
@@ -44841,13 +44823,13 @@
       </c>
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr">
@@ -45008,10 +44990,10 @@
       </c>
       <c r="AX16" t="inlineStr"/>
       <c r="AY16" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
@@ -45815,7 +45797,7 @@
         <v>6834</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -45824,13 +45806,13 @@
         <v>0.7609013754755534</v>
       </c>
       <c r="AY2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.9000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -46004,7 +45986,7 @@
         <v>1833</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -46013,13 +45995,13 @@
         <v>4.391707583196935</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -46188,13 +46170,13 @@
       </c>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.1999999999999886</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
@@ -46364,7 +46346,7 @@
         <v>173.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -46373,13 +46355,13 @@
         <v>2.367205542725181</v>
       </c>
       <c r="AY5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -46548,13 +46530,13 @@
       </c>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr">
@@ -46719,13 +46701,13 @@
       </c>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
@@ -46890,13 +46872,13 @@
       </c>
       <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr">
@@ -47066,7 +47048,7 @@
         <v>1734</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -47081,7 +47063,7 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -47255,7 +47237,7 @@
         <v>3654</v>
       </c>
       <c r="AV10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -47264,13 +47246,13 @@
         <v>-0.9304871373836843</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -47439,13 +47421,13 @@
       </c>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr">
@@ -47610,13 +47592,13 @@
       </c>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-10.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr">
@@ -47781,13 +47763,13 @@
       </c>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.3000000000000114</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr">
@@ -47957,7 +47939,7 @@
         <v>8531</v>
       </c>
       <c r="AV14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -47966,13 +47948,13 @@
         <v>-0.421990387996718</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -48139,13 +48121,13 @@
       </c>
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr">
@@ -48310,13 +48292,13 @@
       </c>
       <c r="AX16" t="inlineStr"/>
       <c r="AY16" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0.4000000000000057</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr">
@@ -48486,7 +48468,7 @@
         <v>6776</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -48495,13 +48477,13 @@
         <v>0.7969303423848828</v>
       </c>
       <c r="AY17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.09999999999999432</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -48816,7 +48798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:BC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49253,7 +49235,7 @@
         <v>1983.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -49262,10 +49244,10 @@
         <v>1.083942525838166</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -49289,24 +49271,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>コナミグループ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6701.T</t>
+          <t>9766.T</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4812</v>
+        <v>21055</v>
       </c>
       <c r="F3" t="n">
-        <v>106.2</v>
+        <v>106.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -49319,91 +49301,91 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>23.7</v>
+        <v>25.3</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7</v>
+        <v>35</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>14.2</v>
+        <v>21.2</v>
       </c>
       <c r="M3" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="N3" t="n">
-        <v>14.5</v>
+        <v>33.6</v>
       </c>
       <c r="O3" t="n">
-        <v>158.6</v>
+        <v>64.2</v>
       </c>
       <c r="P3" t="n">
-        <v>53.4</v>
+        <v>49.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.72</v>
+        <v>-1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>6.08</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>-3.79</v>
       </c>
       <c r="T3" t="n">
-        <v>5.25</v>
+        <v>2.52</v>
       </c>
       <c r="U3" t="n">
-        <v>3.4</v>
+        <v>-3.8</v>
       </c>
       <c r="V3" t="n">
-        <v>28.3</v>
+        <v>18.9</v>
       </c>
       <c r="W3" t="n">
-        <v>15.5</v>
+        <v>3.3</v>
       </c>
       <c r="X3" t="n">
-        <v>1.52</v>
+        <v>-2.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>-6.89</v>
+        <v>-7.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>6021035</v>
+        <v>430435</v>
       </c>
       <c r="AA3" t="n">
-        <v>4739.9</v>
+        <v>21510.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>4440.2</v>
+        <v>19927.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>4598.4</v>
+        <v>20207.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>166.31</v>
+        <v>705.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>4426</v>
+        <v>20210</v>
       </c>
       <c r="AF3" t="n">
-        <v>4668</v>
+        <v>20423</v>
       </c>
       <c r="AG3" t="n">
-        <v>4908</v>
+        <v>21476</v>
       </c>
       <c r="AH3" t="n">
-        <v>4427</v>
+        <v>19371</v>
       </c>
       <c r="AI3" t="n">
-        <v>5534</v>
+        <v>24213</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4562.5</v>
+        <v>19997.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>4403.9</v>
+        <v>20109</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
@@ -49414,11 +49396,7 @@
       <c r="AN3" t="n">
         <v>1.88</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>該当</t>
-        </is>
-      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -49426,38 +49404,38 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>6701_20260914_01</t>
+          <t>9766_20260916_03</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>4682</v>
+        <v>20960</v>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.776591200341727</v>
+        <v>0.4532442748091503</v>
       </c>
       <c r="AY3" t="n">
         <v>20</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -49465,6 +49443,195 @@
         </is>
       </c>
       <c r="BC3" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NEC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6701.T</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4812</v>
+      </c>
+      <c r="F4" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>買い候補</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>83</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-6.89</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6021035</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4739.9</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4440.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4598.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>166.31</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4426</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>4668</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4908</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>4427</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5534</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4562.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>4403.9</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>該当</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>200日線上、75日線上、RSI適正、3か月上昇、6か月上昇、25日線付近、PER良好、ROE良好、配当あり、売上成長、利益成長、値動き安定、下落浅い</t>
+        </is>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>6701_20260914_01</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>4682</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.776591200341727</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>RE-ENTRY</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
@@ -49922,7 +50089,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -49937,7 +50104,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.3999999999999915</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -50107,7 +50274,7 @@
         <v>1771</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -50122,7 +50289,7 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.1000000000000085</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -50292,7 +50459,7 @@
         <v>4985</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -50307,7 +50474,7 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -50477,7 +50644,7 @@
         <v>7158</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -50486,10 +50653,10 @@
         <v>4.638167085778155</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -50662,7 +50829,7 @@
         <v>5618</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -50671,10 +50838,10 @@
         <v>-0.5695977216091164</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -50851,7 +51018,7 @@
         <v>1833</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -50860,13 +51027,13 @@
         <v>4.391707583196935</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.2999999999999972</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -51040,7 +51207,7 @@
         <v>173.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -51049,13 +51216,13 @@
         <v>2.367205542725181</v>
       </c>
       <c r="AY8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.2000000000000028</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -51225,7 +51392,7 @@
         <v>16435</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -51234,10 +51401,10 @@
         <v>5.567386674779429</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
